--- a/data/gravel/Propain Terrel CF 2024.xlsx
+++ b/data/gravel/Propain Terrel CF 2024.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD1C8BAA-446F-3A4E-AF02-87BC25F37C5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFC12FD2-0EC1-1F40-8B78-A331D059379F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="2060" windowWidth="27240" windowHeight="15940" xr2:uid="{7BC12CDB-7FFF-C34B-880D-BB577D883741}"/>
+    <workbookView xWindow="240" yWindow="1220" windowWidth="27460" windowHeight="10620" xr2:uid="{7BC12CDB-7FFF-C34B-880D-BB577D883741}"/>
   </bookViews>
   <sheets>
     <sheet name="Propain Terrel CF 2024" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="147">
   <si>
     <t>brand</t>
   </si>
@@ -71,18 +71,12 @@
     <t>frame weight</t>
   </si>
   <si>
-    <t>UDH</t>
-  </si>
-  <si>
     <t>yes</t>
   </si>
   <si>
     <t>measure range</t>
   </si>
   <si>
-    <t>a10:g33</t>
-  </si>
-  <si>
     <t>frame_size</t>
   </si>
   <si>
@@ -369,13 +363,127 @@
   </si>
   <si>
     <t>XS: 160-170 cm / S: 168-178 cm / M: 175-185 cm / L: 183-193 cm / XL: 190-200 cm</t>
+  </si>
+  <si>
+    <t>udh</t>
+  </si>
+  <si>
+    <t>dropout</t>
+  </si>
+  <si>
+    <t>650B tire max</t>
+  </si>
+  <si>
+    <t>suspension corrected</t>
+  </si>
+  <si>
+    <t>rear axle</t>
+  </si>
+  <si>
+    <t>front axle</t>
+  </si>
+  <si>
+    <t>q-factor</t>
+  </si>
+  <si>
+    <t>seatpost diameter</t>
+  </si>
+  <si>
+    <t>routing shifter</t>
+  </si>
+  <si>
+    <t>routing dropper</t>
+  </si>
+  <si>
+    <t>chainring 1</t>
+  </si>
+  <si>
+    <t>chainring 2</t>
+  </si>
+  <si>
+    <t>bottom bracket</t>
+  </si>
+  <si>
+    <t>mounts inner</t>
+  </si>
+  <si>
+    <t>mounts under</t>
+  </si>
+  <si>
+    <t>mounts top</t>
+  </si>
+  <si>
+    <t>mounts fork</t>
+  </si>
+  <si>
+    <t>mounts fender rear</t>
+  </si>
+  <si>
+    <t>mounts fender front</t>
+  </si>
+  <si>
+    <t>mounts rack</t>
+  </si>
+  <si>
+    <t>rotor max front</t>
+  </si>
+  <si>
+    <t>rotor max rear</t>
+  </si>
+  <si>
+    <t>frameset</t>
+  </si>
+  <si>
+    <t>currency</t>
+  </si>
+  <si>
+    <t>routing dynamo</t>
+  </si>
+  <si>
+    <t>T47</t>
+  </si>
+  <si>
+    <t>base build</t>
+  </si>
+  <si>
+    <t>us</t>
+  </si>
+  <si>
+    <t>internal</t>
+  </si>
+  <si>
+    <t>front derailleur</t>
+  </si>
+  <si>
+    <t>fork suspension</t>
+  </si>
+  <si>
+    <t>stem suspension</t>
+  </si>
+  <si>
+    <t>rear suspension</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>internal storage</t>
+  </si>
+  <si>
+    <t>a10:g34</t>
+  </si>
+  <si>
+    <t>700c width max</t>
+  </si>
+  <si>
+    <t>ISO ASTM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -387,6 +495,18 @@
       <sz val="14"/>
       <color theme="1"/>
       <name val="Futura Medium"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Futura Medium"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Futura"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -409,10 +529,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -747,15 +875,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0B39A2D-4337-6D49-BF11-5DE928D47A13}">
-  <dimension ref="A1:Q36"/>
+  <dimension ref="A1:AH37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="27" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="27" style="1"/>
     <col min="3" max="7" width="13.83203125" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="27" style="1"/>
+    <col min="8" max="30" width="14.6640625" style="1" customWidth="1"/>
+    <col min="31" max="16384" width="27" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -763,7 +892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -771,7 +900,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -779,7 +908,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -787,7 +916,7 @@
         <v>45851</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -795,82 +924,255 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:34" s="3" customFormat="1" ht="44" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="P6" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q6" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="R6" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="S6" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="T6" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="U6" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="V6" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="W6" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="X6" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y6" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="Z6" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA6" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB6" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="AC6" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="AD6" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AE6" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="AF6" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG6" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="AH6" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="B7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C7" s="1">
+        <v>0</v>
+      </c>
+      <c r="D7" s="1">
+        <v>50</v>
+      </c>
+      <c r="F7" s="1">
+        <v>40</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J7" s="1">
+        <v>142</v>
+      </c>
+      <c r="K7" s="1">
+        <v>100</v>
+      </c>
+      <c r="M7" s="1">
+        <v>27.2</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="U7" s="1">
+        <v>2</v>
+      </c>
+      <c r="V7" s="1">
+        <v>1</v>
+      </c>
+      <c r="W7" s="1">
+        <v>1</v>
+      </c>
+      <c r="X7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC7" s="1">
+        <v>160</v>
+      </c>
+      <c r="AD7" s="1">
+        <v>160</v>
+      </c>
+      <c r="AE7" s="1">
+        <v>1999</v>
+      </c>
+      <c r="AF7" s="1">
+        <v>2899</v>
+      </c>
+      <c r="AG7" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AH7" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="B9" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B10" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="G10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="L10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="B11" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="O10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="P10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q10" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="C11" s="1">
         <v>470</v>
@@ -888,30 +1190,30 @@
         <v>570</v>
       </c>
       <c r="L11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N11" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M11" s="1" t="s">
+      <c r="O11" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N11" s="1" t="s">
+      <c r="P11" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="O11" s="1" t="s">
+      <c r="Q11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="P11" s="1" t="s">
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="Q11" s="1" t="s">
+      <c r="B12" s="1" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="C12" s="1">
         <v>45</v>
@@ -929,30 +1231,30 @@
         <v>45</v>
       </c>
       <c r="L12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="M12" s="1" t="s">
+      <c r="B13" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="O12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="P12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q12" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="C13" s="1">
         <v>425</v>
@@ -970,30 +1272,30 @@
         <v>425</v>
       </c>
       <c r="L13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M13" s="1" t="s">
+      <c r="B14" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="O13" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="P13" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q13" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="C14" s="1">
         <v>98</v>
@@ -1011,30 +1313,30 @@
         <v>177</v>
       </c>
       <c r="L14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="N14" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="M14" s="1" t="s">
+      <c r="O14" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="N14" s="1" t="s">
+      <c r="P14" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="O14" s="1" t="s">
+      <c r="Q14" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="P14" s="1" t="s">
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="Q14" s="1" t="s">
+      <c r="B15" s="1" t="s">
         <v>41</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="C15" s="1">
         <v>382</v>
@@ -1052,30 +1354,30 @@
         <v>430</v>
       </c>
       <c r="L15" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N15" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="M15" s="1" t="s">
+      <c r="O15" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="N15" s="1" t="s">
+      <c r="P15" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="O15" s="1" t="s">
+      <c r="Q15" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="P15" s="1" t="s">
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="Q15" s="1" t="s">
+      <c r="B16" s="1" t="s">
         <v>48</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="C16" s="1">
         <v>554</v>
@@ -1093,30 +1395,30 @@
         <v>632</v>
       </c>
       <c r="L16" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="N16" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="M16" s="1" t="s">
+      <c r="O16" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="N16" s="1" t="s">
+      <c r="P16" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="O16" s="1" t="s">
+      <c r="Q16" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="P16" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q16" s="1" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C17" s="1">
         <v>69.5</v>
@@ -1134,30 +1436,30 @@
         <v>71.5</v>
       </c>
       <c r="L17" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="N17" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="M17" s="1" t="s">
+      <c r="O17" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="N17" s="1" t="s">
+      <c r="P17" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="O17" s="1" t="s">
+      <c r="Q17" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="P17" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q17" s="1" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C18" s="1">
         <v>74.3</v>
@@ -1175,30 +1477,30 @@
         <v>73.5</v>
       </c>
       <c r="L18" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="N18" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="M18" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="O18" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C19" s="1">
         <v>538</v>
@@ -1216,30 +1518,30 @@
         <v>617</v>
       </c>
       <c r="L19" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="N19" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="M19" s="1" t="s">
+      <c r="O19" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="N19" s="1" t="s">
+      <c r="P19" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="O19" s="1" t="s">
+      <c r="Q19" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="P19" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q19" s="1" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C20" s="1">
         <v>77</v>
@@ -1257,30 +1559,30 @@
         <v>72</v>
       </c>
       <c r="L20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="N20" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="M20" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>77</v>
-      </c>
       <c r="O20" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C21" s="1">
         <v>287</v>
@@ -1298,30 +1600,30 @@
         <v>292</v>
       </c>
       <c r="L21" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="N21" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="M21" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>81</v>
-      </c>
       <c r="O21" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C22" s="1">
         <v>435</v>
@@ -1339,30 +1641,30 @@
         <v>435</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C23" s="1">
         <v>1037</v>
@@ -1380,30 +1682,30 @@
         <v>1094</v>
       </c>
       <c r="L23" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="N23" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="M23" s="1" t="s">
+      <c r="O23" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="N23" s="1" t="s">
+      <c r="P23" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="O23" s="1" t="s">
+      <c r="Q23" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="P23" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q23" s="1" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C24" s="1">
         <v>787</v>
@@ -1421,30 +1723,30 @@
         <v>862</v>
       </c>
       <c r="L24" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="N24" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="M24" s="1" t="s">
+      <c r="O24" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="N24" s="1" t="s">
+      <c r="P24" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="O24" s="1" t="s">
+      <c r="Q24" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="P24" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q24" s="1" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C25" s="1">
         <v>441.76237959999997</v>
@@ -1464,95 +1766,83 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C26" s="1">
-        <v>420</v>
-      </c>
-      <c r="D26" s="1">
-        <v>420</v>
+        <v>10</v>
       </c>
       <c r="E26" s="1">
-        <v>440</v>
-      </c>
-      <c r="F26" s="1">
-        <v>440</v>
-      </c>
-      <c r="G26" s="1">
-        <v>460</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C27" s="1">
-        <v>70</v>
+        <v>420</v>
       </c>
       <c r="D27" s="1">
-        <v>80</v>
+        <v>420</v>
       </c>
       <c r="E27" s="1">
-        <v>80</v>
+        <v>440</v>
       </c>
       <c r="F27" s="1">
-        <v>90</v>
+        <v>440</v>
       </c>
       <c r="G27" s="1">
-        <v>100</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>103</v>
+        <v>460</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
+      </c>
+      <c r="C28" s="1">
+        <v>70</v>
+      </c>
+      <c r="D28" s="1">
+        <v>80</v>
+      </c>
+      <c r="E28" s="1">
+        <v>80</v>
+      </c>
+      <c r="F28" s="1">
+        <v>90</v>
+      </c>
+      <c r="G28" s="1">
+        <v>100</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C29" s="1">
-        <v>700</v>
-      </c>
-      <c r="D29" s="1">
-        <v>700</v>
-      </c>
-      <c r="E29" s="1">
-        <v>700</v>
-      </c>
-      <c r="F29" s="1">
-        <v>700</v>
-      </c>
-      <c r="G29" s="1">
-        <v>700</v>
+        <v>102</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C30" s="1">
-        <v>50</v>
+        <v>700</v>
       </c>
       <c r="D30" s="1">
-        <v>50</v>
+        <v>700</v>
       </c>
       <c r="E30" s="1">
-        <v>50</v>
+        <v>700</v>
       </c>
       <c r="F30" s="1">
-        <v>50</v>
+        <v>700</v>
       </c>
       <c r="G30" s="1">
-        <v>50</v>
+        <v>700</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C31" s="1">
         <v>50</v>
@@ -1572,89 +1862,109 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C32" s="1">
+        <v>50</v>
+      </c>
+      <c r="D32" s="1">
+        <v>50</v>
+      </c>
+      <c r="E32" s="1">
+        <v>50</v>
+      </c>
+      <c r="F32" s="1">
+        <v>50</v>
+      </c>
+      <c r="G32" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C33" s="1">
         <v>160</v>
       </c>
-      <c r="D32" s="1">
-        <f>AVERAGE(D34,C35)</f>
+      <c r="D33" s="1">
+        <f>AVERAGE(D35,C36)</f>
         <v>169</v>
       </c>
-      <c r="E32" s="1">
-        <f t="shared" ref="E32:G32" si="0">AVERAGE(E34,D35)</f>
+      <c r="E33" s="1">
+        <f t="shared" ref="E33:F33" si="0">AVERAGE(E35,D36)</f>
         <v>176.5</v>
       </c>
-      <c r="F32" s="1">
+      <c r="F33" s="1">
         <f t="shared" si="0"/>
         <v>184</v>
       </c>
-      <c r="G32" s="1">
-        <f t="shared" si="0"/>
+      <c r="G33" s="1">
+        <f>AVERAGE(G35,F36)</f>
         <v>191.5</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C33" s="1">
-        <f>D32</f>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C34" s="1">
+        <f>D33</f>
         <v>169</v>
       </c>
-      <c r="D33" s="1">
-        <f t="shared" ref="D33:F33" si="1">E32</f>
+      <c r="D34" s="1">
+        <f t="shared" ref="D34:E34" si="1">E33</f>
         <v>176.5</v>
       </c>
-      <c r="E33" s="1">
+      <c r="E34" s="1">
         <f t="shared" si="1"/>
         <v>184</v>
       </c>
-      <c r="F33" s="1">
-        <f t="shared" si="1"/>
+      <c r="F34" s="1">
+        <f>G33</f>
         <v>191.5</v>
       </c>
-      <c r="G33" s="1">
+      <c r="G34" s="1">
         <v>200</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C34" s="1">
-        <v>160</v>
-      </c>
-      <c r="D34" s="1">
-        <v>168</v>
-      </c>
-      <c r="E34" s="1">
-        <v>175</v>
-      </c>
-      <c r="F34" s="1">
-        <v>183</v>
-      </c>
-      <c r="G34" s="1">
-        <v>190</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C35" s="1">
+        <v>160</v>
+      </c>
+      <c r="D35" s="1">
+        <v>168</v>
+      </c>
+      <c r="E35" s="1">
+        <v>175</v>
+      </c>
+      <c r="F35" s="1">
+        <v>183</v>
+      </c>
+      <c r="G35" s="1">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C36" s="1">
         <v>170</v>
       </c>
-      <c r="D35" s="1">
+      <c r="D36" s="1">
         <v>178</v>
       </c>
-      <c r="E35" s="1">
+      <c r="E36" s="1">
         <v>185</v>
       </c>
-      <c r="F35" s="1">
+      <c r="F36" s="1">
         <v>193</v>
       </c>
-      <c r="G35" s="1">
+      <c r="G36" s="1">
         <v>200</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
-        <v>110</v>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Propain Terrel CF 2024.xlsx
+++ b/data/gravel/Propain Terrel CF 2024.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel copy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D866175-955E-6E4E-83FE-8C0780235B96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F8C0B2D-A345-3644-AB98-422D5A037A08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="21840" windowHeight="15120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="117">
   <si>
     <t>brand</t>
   </si>
@@ -353,6 +353,24 @@
   </si>
   <si>
     <t>trail</t>
+  </si>
+  <si>
+    <t>class</t>
+  </si>
+  <si>
+    <t>gravel</t>
+  </si>
+  <si>
+    <t>handlebar</t>
+  </si>
+  <si>
+    <t>drop bar</t>
+  </si>
+  <si>
+    <t>fork</t>
+  </si>
+  <si>
+    <t>rigid</t>
   </si>
 </sst>
 </file>
@@ -691,7 +709,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1259,229 +1277,232 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>58</v>
+        <v>111</v>
       </c>
       <c r="B35" t="s">
-        <v>59</v>
+        <v>112</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>60</v>
+        <v>113</v>
       </c>
       <c r="B36" t="s">
-        <v>61</v>
+        <v>114</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>62</v>
+        <v>115</v>
       </c>
       <c r="B37" t="s">
-        <v>63</v>
+        <v>116</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B38" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>66</v>
+        <v>60</v>
+      </c>
+      <c r="B39" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B40" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B41" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>70</v>
-      </c>
-      <c r="B42" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B43" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B44" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B45" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B46" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>79</v>
+        <v>73</v>
+      </c>
+      <c r="B47" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B48" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B49" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>84</v>
+        <v>80</v>
+      </c>
+      <c r="B51" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B52" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>87</v>
-      </c>
-      <c r="B53" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>88</v>
-      </c>
-      <c r="B54" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B55" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B56" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>92</v>
+        <v>88</v>
+      </c>
+      <c r="B57" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B58" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B59" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>96</v>
-      </c>
-      <c r="B60" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B61" t="s">
-        <v>97</v>
+        <v>61</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B62" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B63" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>101</v>
+        <v>98</v>
+      </c>
+      <c r="B64" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B65" t="s">
         <v>61</v>
@@ -1489,30 +1510,51 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B66" t="s">
-        <v>104</v>
+        <v>61</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>105</v>
-      </c>
-      <c r="B67" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>107</v>
+        <v>102</v>
+      </c>
+      <c r="B68" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
+        <v>103</v>
+      </c>
+      <c r="B69" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>105</v>
+      </c>
+      <c r="B70" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
         <v>108</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B72" t="s">
         <v>109</v>
       </c>
     </row>
